--- a/templates/欧代标签-灵羽-130.xlsx
+++ b/templates/欧代标签-灵羽-130.xlsx
@@ -1779,8 +1779,10 @@
       <c r="B1" s="29"/>
     </row>
     <row r="2" s="25" customFormat="1" ht="18" customHeight="1" spans="1:8">
-      <c r="A2" s="30" t="s">
-        <v>1</v>
+      <c r="A2" s="30" t="inlineStr">
+        <is>
+          <t>ItemNo：</t>
+        </is>
       </c>
       <c r="B2" s="31"/>
     </row>
@@ -1890,8 +1892,10 @@
       </c>
     </row>
     <row r="2" s="2" customFormat="1" ht="18" customHeight="1" spans="1:8">
-      <c r="A2" s="7" t="s">
-        <v>1</v>
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>ItemNo：</t>
+        </is>
       </c>
       <c r="B2" s="8" t="s">
         <v>17</v>
